--- a/VerveStacks_BRA_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_BRA_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{986C5C05-BB39-4F7B-B153-709260D8424A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{207DB546-013A-40B8-8105-ECC3F2F32CBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1844" uniqueCount="503">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1764" uniqueCount="487">
   <si>
     <t>PSET_PN</t>
   </si>
@@ -1339,16 +1339,16 @@
     <t>e_demand,ev_battery,H2prd_Elc_PEM,H2prd_Elc_ALK</t>
   </si>
   <si>
-    <t>w172071437-440</t>
-  </si>
-  <si>
-    <t>at grid node - w172071437-440</t>
-  </si>
-  <si>
-    <t>w174852067-440</t>
-  </si>
-  <si>
-    <t>at grid node - w174852067-440</t>
+    <t>w202622375-765</t>
+  </si>
+  <si>
+    <t>at grid node - w202622375-765</t>
+  </si>
+  <si>
+    <t>w271191830-500</t>
+  </si>
+  <si>
+    <t>at grid node - w271191830-500</t>
   </si>
   <si>
     <t>w348815398-500</t>
@@ -1381,24 +1381,18 @@
     <t>at grid node - w969586211-525</t>
   </si>
   <si>
+    <t>BR669-500</t>
+  </si>
+  <si>
+    <t>at grid node - BR669-500</t>
+  </si>
+  <si>
     <t>BR686-500</t>
   </si>
   <si>
     <t>at grid node - BR686-500</t>
   </si>
   <si>
-    <t>BR746-500</t>
-  </si>
-  <si>
-    <t>at grid node - BR746-500</t>
-  </si>
-  <si>
-    <t>BR708-440</t>
-  </si>
-  <si>
-    <t>at grid node - BR708-440</t>
-  </si>
-  <si>
     <t>BR656-500</t>
   </si>
   <si>
@@ -1417,12 +1411,6 @@
     <t>at grid node - BR208-500</t>
   </si>
   <si>
-    <t>BR710-440</t>
-  </si>
-  <si>
-    <t>at grid node - BR710-440</t>
-  </si>
-  <si>
     <t>BR744-440</t>
   </si>
   <si>
@@ -1447,12 +1435,6 @@
     <t>at grid node - BR122-500</t>
   </si>
   <si>
-    <t>BR721-440</t>
-  </si>
-  <si>
-    <t>at grid node - BR721-440</t>
-  </si>
-  <si>
     <t>BR360-500</t>
   </si>
   <si>
@@ -1483,12 +1465,6 @@
     <t>at grid node - w206109551-500</t>
   </si>
   <si>
-    <t>BR80-500</t>
-  </si>
-  <si>
-    <t>at grid node - BR80-500</t>
-  </si>
-  <si>
     <t>BR643-500</t>
   </si>
   <si>
@@ -1501,12 +1477,6 @@
     <t>at grid node - BR909-500</t>
   </si>
   <si>
-    <t>BR903-500</t>
-  </si>
-  <si>
-    <t>at grid node - BR903-500</t>
-  </si>
-  <si>
     <t>BR862-500</t>
   </si>
   <si>
@@ -1529,24 +1499,6 @@
   </si>
   <si>
     <t>at grid node - BR947-525</t>
-  </si>
-  <si>
-    <t>BR355-500</t>
-  </si>
-  <si>
-    <t>at grid node - BR355-500</t>
-  </si>
-  <si>
-    <t>BR851-500</t>
-  </si>
-  <si>
-    <t>at grid node - BR851-500</t>
-  </si>
-  <si>
-    <t>BR787-525</t>
-  </si>
-  <si>
-    <t>at grid node - BR787-525</t>
   </si>
 </sst>
 </file>
@@ -2053,10 +2005,10 @@
         <v>78</v>
       </c>
       <c r="R12" t="s">
-        <v>106</v>
+        <v>261</v>
       </c>
       <c r="S12" t="s">
-        <v>107</v>
+        <v>262</v>
       </c>
       <c r="T12" t="s">
         <v>432</v>
@@ -2103,10 +2055,10 @@
         <v>78</v>
       </c>
       <c r="R13" t="s">
-        <v>433</v>
+        <v>106</v>
       </c>
       <c r="S13" t="s">
-        <v>434</v>
+        <v>107</v>
       </c>
       <c r="T13" t="s">
         <v>432</v>
@@ -2153,10 +2105,10 @@
         <v>78</v>
       </c>
       <c r="R14" t="s">
-        <v>320</v>
+        <v>205</v>
       </c>
       <c r="S14" t="s">
-        <v>321</v>
+        <v>206</v>
       </c>
       <c r="T14" t="s">
         <v>432</v>
@@ -2203,10 +2155,10 @@
         <v>78</v>
       </c>
       <c r="R15" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="S15" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="T15" t="s">
         <v>432</v>
@@ -2253,10 +2205,10 @@
         <v>78</v>
       </c>
       <c r="R16" t="s">
-        <v>205</v>
+        <v>435</v>
       </c>
       <c r="S16" t="s">
-        <v>206</v>
+        <v>436</v>
       </c>
       <c r="T16" t="s">
         <v>432</v>
@@ -2403,10 +2355,10 @@
         <v>78</v>
       </c>
       <c r="R19" t="s">
-        <v>130</v>
+        <v>390</v>
       </c>
       <c r="S19" t="s">
-        <v>131</v>
+        <v>391</v>
       </c>
       <c r="T19" t="s">
         <v>432</v>
@@ -2453,10 +2405,10 @@
         <v>78</v>
       </c>
       <c r="R20" t="s">
-        <v>390</v>
+        <v>140</v>
       </c>
       <c r="S20" t="s">
-        <v>391</v>
+        <v>141</v>
       </c>
       <c r="T20" t="s">
         <v>432</v>
@@ -2503,10 +2455,10 @@
         <v>78</v>
       </c>
       <c r="R21" t="s">
-        <v>140</v>
+        <v>439</v>
       </c>
       <c r="S21" t="s">
-        <v>141</v>
+        <v>440</v>
       </c>
       <c r="T21" t="s">
         <v>432</v>
@@ -2553,10 +2505,10 @@
         <v>78</v>
       </c>
       <c r="R22" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="S22" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="T22" t="s">
         <v>432</v>
@@ -2603,10 +2555,10 @@
         <v>78</v>
       </c>
       <c r="R23" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="S23" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="T23" t="s">
         <v>432</v>
@@ -2653,10 +2605,10 @@
         <v>78</v>
       </c>
       <c r="R24" t="s">
-        <v>443</v>
+        <v>104</v>
       </c>
       <c r="S24" t="s">
-        <v>444</v>
+        <v>105</v>
       </c>
       <c r="T24" t="s">
         <v>432</v>
@@ -2703,10 +2655,10 @@
         <v>78</v>
       </c>
       <c r="R25" t="s">
-        <v>104</v>
+        <v>445</v>
       </c>
       <c r="S25" t="s">
-        <v>105</v>
+        <v>446</v>
       </c>
       <c r="T25" t="s">
         <v>432</v>
@@ -2753,10 +2705,10 @@
         <v>78</v>
       </c>
       <c r="R26" t="s">
-        <v>445</v>
+        <v>185</v>
       </c>
       <c r="S26" t="s">
-        <v>446</v>
+        <v>186</v>
       </c>
       <c r="T26" t="s">
         <v>432</v>
@@ -2803,10 +2755,10 @@
         <v>78</v>
       </c>
       <c r="R27" t="s">
-        <v>185</v>
+        <v>447</v>
       </c>
       <c r="S27" t="s">
-        <v>186</v>
+        <v>448</v>
       </c>
       <c r="T27" t="s">
         <v>432</v>
@@ -2853,10 +2805,10 @@
         <v>78</v>
       </c>
       <c r="R28" t="s">
-        <v>108</v>
+        <v>449</v>
       </c>
       <c r="S28" t="s">
-        <v>109</v>
+        <v>450</v>
       </c>
       <c r="T28" t="s">
         <v>432</v>
@@ -2903,10 +2855,10 @@
         <v>78</v>
       </c>
       <c r="R29" t="s">
-        <v>110</v>
+        <v>338</v>
       </c>
       <c r="S29" t="s">
-        <v>111</v>
+        <v>339</v>
       </c>
       <c r="T29" t="s">
         <v>432</v>
@@ -2953,10 +2905,10 @@
         <v>78</v>
       </c>
       <c r="R30" t="s">
-        <v>193</v>
+        <v>340</v>
       </c>
       <c r="S30" t="s">
-        <v>194</v>
+        <v>341</v>
       </c>
       <c r="T30" t="s">
         <v>432</v>
@@ -3003,10 +2955,10 @@
         <v>78</v>
       </c>
       <c r="R31" t="s">
-        <v>447</v>
+        <v>422</v>
       </c>
       <c r="S31" t="s">
-        <v>448</v>
+        <v>423</v>
       </c>
       <c r="T31" t="s">
         <v>432</v>
@@ -3053,10 +3005,10 @@
         <v>78</v>
       </c>
       <c r="R32" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="S32" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="T32" t="s">
         <v>432</v>
@@ -3103,10 +3055,10 @@
         <v>78</v>
       </c>
       <c r="R33" t="s">
-        <v>422</v>
+        <v>223</v>
       </c>
       <c r="S33" t="s">
-        <v>423</v>
+        <v>224</v>
       </c>
       <c r="T33" t="s">
         <v>432</v>
@@ -3153,10 +3105,10 @@
         <v>78</v>
       </c>
       <c r="R34" t="s">
-        <v>449</v>
+        <v>96</v>
       </c>
       <c r="S34" t="s">
-        <v>450</v>
+        <v>97</v>
       </c>
       <c r="T34" t="s">
         <v>432</v>
@@ -3203,10 +3155,10 @@
         <v>78</v>
       </c>
       <c r="R35" t="s">
-        <v>346</v>
+        <v>451</v>
       </c>
       <c r="S35" t="s">
-        <v>347</v>
+        <v>452</v>
       </c>
       <c r="T35" t="s">
         <v>432</v>
@@ -3253,10 +3205,10 @@
         <v>78</v>
       </c>
       <c r="R36" t="s">
-        <v>259</v>
+        <v>163</v>
       </c>
       <c r="S36" t="s">
-        <v>260</v>
+        <v>164</v>
       </c>
       <c r="T36" t="s">
         <v>432</v>
@@ -3303,10 +3255,10 @@
         <v>78</v>
       </c>
       <c r="R37" t="s">
-        <v>364</v>
+        <v>86</v>
       </c>
       <c r="S37" t="s">
-        <v>365</v>
+        <v>87</v>
       </c>
       <c r="T37" t="s">
         <v>432</v>
@@ -3353,10 +3305,10 @@
         <v>78</v>
       </c>
       <c r="R38" t="s">
-        <v>322</v>
+        <v>207</v>
       </c>
       <c r="S38" t="s">
-        <v>323</v>
+        <v>208</v>
       </c>
       <c r="T38" t="s">
         <v>432</v>
@@ -3403,10 +3355,10 @@
         <v>78</v>
       </c>
       <c r="R39" t="s">
-        <v>132</v>
+        <v>290</v>
       </c>
       <c r="S39" t="s">
-        <v>133</v>
+        <v>291</v>
       </c>
       <c r="T39" t="s">
         <v>432</v>
@@ -3453,10 +3405,10 @@
         <v>78</v>
       </c>
       <c r="R40" t="s">
-        <v>352</v>
+        <v>221</v>
       </c>
       <c r="S40" t="s">
-        <v>353</v>
+        <v>222</v>
       </c>
       <c r="T40" t="s">
         <v>432</v>
@@ -3503,10 +3455,10 @@
         <v>78</v>
       </c>
       <c r="R41" t="s">
-        <v>451</v>
+        <v>156</v>
       </c>
       <c r="S41" t="s">
-        <v>452</v>
+        <v>157</v>
       </c>
       <c r="T41" t="s">
         <v>432</v>
@@ -3553,10 +3505,10 @@
         <v>78</v>
       </c>
       <c r="R42" t="s">
-        <v>96</v>
+        <v>360</v>
       </c>
       <c r="S42" t="s">
-        <v>97</v>
+        <v>361</v>
       </c>
       <c r="T42" t="s">
         <v>432</v>
@@ -3653,10 +3605,10 @@
         <v>78</v>
       </c>
       <c r="R44" t="s">
-        <v>163</v>
+        <v>455</v>
       </c>
       <c r="S44" t="s">
-        <v>164</v>
+        <v>456</v>
       </c>
       <c r="T44" t="s">
         <v>432</v>
@@ -3703,10 +3655,10 @@
         <v>78</v>
       </c>
       <c r="R45" t="s">
-        <v>86</v>
+        <v>287</v>
       </c>
       <c r="S45" t="s">
-        <v>87</v>
+        <v>288</v>
       </c>
       <c r="T45" t="s">
         <v>432</v>
@@ -3753,10 +3705,10 @@
         <v>78</v>
       </c>
       <c r="R46" t="s">
-        <v>207</v>
+        <v>358</v>
       </c>
       <c r="S46" t="s">
-        <v>208</v>
+        <v>359</v>
       </c>
       <c r="T46" t="s">
         <v>432</v>
@@ -3803,10 +3755,10 @@
         <v>78</v>
       </c>
       <c r="R47" t="s">
-        <v>360</v>
+        <v>134</v>
       </c>
       <c r="S47" t="s">
-        <v>361</v>
+        <v>135</v>
       </c>
       <c r="T47" t="s">
         <v>432</v>
@@ -3853,10 +3805,10 @@
         <v>78</v>
       </c>
       <c r="R48" t="s">
-        <v>455</v>
+        <v>98</v>
       </c>
       <c r="S48" t="s">
-        <v>456</v>
+        <v>99</v>
       </c>
       <c r="T48" t="s">
         <v>432</v>
@@ -3891,10 +3843,10 @@
         <v>78</v>
       </c>
       <c r="R49" t="s">
-        <v>136</v>
+        <v>306</v>
       </c>
       <c r="S49" t="s">
-        <v>137</v>
+        <v>307</v>
       </c>
       <c r="T49" t="s">
         <v>432</v>
@@ -3929,10 +3881,10 @@
         <v>78</v>
       </c>
       <c r="R50" t="s">
-        <v>457</v>
+        <v>177</v>
       </c>
       <c r="S50" t="s">
-        <v>458</v>
+        <v>178</v>
       </c>
       <c r="T50" t="s">
         <v>432</v>
@@ -3967,10 +3919,10 @@
         <v>78</v>
       </c>
       <c r="R51" t="s">
-        <v>459</v>
+        <v>255</v>
       </c>
       <c r="S51" t="s">
-        <v>460</v>
+        <v>256</v>
       </c>
       <c r="T51" t="s">
         <v>432</v>
@@ -4005,10 +3957,10 @@
         <v>78</v>
       </c>
       <c r="R52" t="s">
-        <v>287</v>
+        <v>430</v>
       </c>
       <c r="S52" t="s">
-        <v>288</v>
+        <v>431</v>
       </c>
       <c r="T52" t="s">
         <v>432</v>
@@ -4043,10 +3995,10 @@
         <v>78</v>
       </c>
       <c r="R53" t="s">
-        <v>304</v>
+        <v>354</v>
       </c>
       <c r="S53" t="s">
-        <v>305</v>
+        <v>355</v>
       </c>
       <c r="T53" t="s">
         <v>432</v>
@@ -4081,10 +4033,10 @@
         <v>78</v>
       </c>
       <c r="R54" t="s">
-        <v>358</v>
+        <v>237</v>
       </c>
       <c r="S54" t="s">
-        <v>359</v>
+        <v>238</v>
       </c>
       <c r="T54" t="s">
         <v>432</v>
@@ -4119,10 +4071,10 @@
         <v>78</v>
       </c>
       <c r="R55" t="s">
-        <v>134</v>
+        <v>296</v>
       </c>
       <c r="S55" t="s">
-        <v>135</v>
+        <v>297</v>
       </c>
       <c r="T55" t="s">
         <v>432</v>
@@ -4157,10 +4109,10 @@
         <v>78</v>
       </c>
       <c r="R56" t="s">
-        <v>98</v>
+        <v>215</v>
       </c>
       <c r="S56" t="s">
-        <v>99</v>
+        <v>216</v>
       </c>
       <c r="T56" t="s">
         <v>432</v>
@@ -4195,10 +4147,10 @@
         <v>78</v>
       </c>
       <c r="R57" t="s">
-        <v>306</v>
+        <v>457</v>
       </c>
       <c r="S57" t="s">
-        <v>307</v>
+        <v>458</v>
       </c>
       <c r="T57" t="s">
         <v>432</v>
@@ -4233,10 +4185,10 @@
         <v>78</v>
       </c>
       <c r="R58" t="s">
-        <v>255</v>
+        <v>459</v>
       </c>
       <c r="S58" t="s">
-        <v>256</v>
+        <v>460</v>
       </c>
       <c r="T58" t="s">
         <v>432</v>
@@ -4271,10 +4223,10 @@
         <v>78</v>
       </c>
       <c r="R59" t="s">
-        <v>267</v>
+        <v>461</v>
       </c>
       <c r="S59" t="s">
-        <v>268</v>
+        <v>462</v>
       </c>
       <c r="T59" t="s">
         <v>432</v>
@@ -4309,10 +4261,10 @@
         <v>78</v>
       </c>
       <c r="R60" t="s">
-        <v>354</v>
+        <v>463</v>
       </c>
       <c r="S60" t="s">
-        <v>355</v>
+        <v>464</v>
       </c>
       <c r="T60" t="s">
         <v>432</v>
@@ -4347,10 +4299,10 @@
         <v>78</v>
       </c>
       <c r="R61" t="s">
-        <v>237</v>
+        <v>199</v>
       </c>
       <c r="S61" t="s">
-        <v>238</v>
+        <v>200</v>
       </c>
       <c r="T61" t="s">
         <v>432</v>
@@ -4385,10 +4337,10 @@
         <v>78</v>
       </c>
       <c r="R62" t="s">
-        <v>296</v>
+        <v>370</v>
       </c>
       <c r="S62" t="s">
-        <v>297</v>
+        <v>371</v>
       </c>
       <c r="T62" t="s">
         <v>432</v>
@@ -4423,10 +4375,10 @@
         <v>78</v>
       </c>
       <c r="R63" t="s">
-        <v>215</v>
+        <v>122</v>
       </c>
       <c r="S63" t="s">
-        <v>216</v>
+        <v>123</v>
       </c>
       <c r="T63" t="s">
         <v>432</v>
@@ -4461,10 +4413,10 @@
         <v>78</v>
       </c>
       <c r="R64" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="S64" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="T64" t="s">
         <v>432</v>
@@ -4499,10 +4451,10 @@
         <v>78</v>
       </c>
       <c r="R65" t="s">
-        <v>348</v>
+        <v>467</v>
       </c>
       <c r="S65" t="s">
-        <v>349</v>
+        <v>468</v>
       </c>
       <c r="T65" t="s">
         <v>432</v>
@@ -4537,10 +4489,10 @@
         <v>78</v>
       </c>
       <c r="R66" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="S66" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="T66" t="s">
         <v>432</v>
@@ -4575,10 +4527,10 @@
         <v>78</v>
       </c>
       <c r="R67" t="s">
-        <v>465</v>
+        <v>169</v>
       </c>
       <c r="S67" t="s">
-        <v>466</v>
+        <v>170</v>
       </c>
       <c r="T67" t="s">
         <v>432</v>
@@ -4613,10 +4565,10 @@
         <v>78</v>
       </c>
       <c r="R68" t="s">
-        <v>467</v>
+        <v>328</v>
       </c>
       <c r="S68" t="s">
-        <v>468</v>
+        <v>329</v>
       </c>
       <c r="T68" t="s">
         <v>432</v>
@@ -4651,10 +4603,10 @@
         <v>78</v>
       </c>
       <c r="R69" t="s">
-        <v>199</v>
+        <v>161</v>
       </c>
       <c r="S69" t="s">
-        <v>200</v>
+        <v>162</v>
       </c>
       <c r="T69" t="s">
         <v>432</v>
@@ -4689,10 +4641,10 @@
         <v>78</v>
       </c>
       <c r="R70" t="s">
-        <v>469</v>
+        <v>227</v>
       </c>
       <c r="S70" t="s">
-        <v>470</v>
+        <v>228</v>
       </c>
       <c r="T70" t="s">
         <v>432</v>
@@ -4727,10 +4679,10 @@
         <v>78</v>
       </c>
       <c r="R71" t="s">
-        <v>116</v>
+        <v>412</v>
       </c>
       <c r="S71" t="s">
-        <v>117</v>
+        <v>413</v>
       </c>
       <c r="T71" t="s">
         <v>432</v>
@@ -4765,10 +4717,10 @@
         <v>78</v>
       </c>
       <c r="R72" t="s">
-        <v>122</v>
+        <v>471</v>
       </c>
       <c r="S72" t="s">
-        <v>123</v>
+        <v>472</v>
       </c>
       <c r="T72" t="s">
         <v>432</v>
@@ -4803,10 +4755,10 @@
         <v>78</v>
       </c>
       <c r="R73" t="s">
-        <v>471</v>
+        <v>235</v>
       </c>
       <c r="S73" t="s">
-        <v>472</v>
+        <v>236</v>
       </c>
       <c r="T73" t="s">
         <v>432</v>
@@ -4917,10 +4869,10 @@
         <v>78</v>
       </c>
       <c r="R76" t="s">
-        <v>169</v>
+        <v>477</v>
       </c>
       <c r="S76" t="s">
-        <v>170</v>
+        <v>478</v>
       </c>
       <c r="T76" t="s">
         <v>432</v>
@@ -4955,10 +4907,10 @@
         <v>78</v>
       </c>
       <c r="R77" t="s">
-        <v>328</v>
+        <v>479</v>
       </c>
       <c r="S77" t="s">
-        <v>329</v>
+        <v>480</v>
       </c>
       <c r="T77" t="s">
         <v>432</v>
@@ -4993,10 +4945,10 @@
         <v>78</v>
       </c>
       <c r="R78" t="s">
-        <v>161</v>
+        <v>481</v>
       </c>
       <c r="S78" t="s">
-        <v>162</v>
+        <v>482</v>
       </c>
       <c r="T78" t="s">
         <v>432</v>
@@ -5031,10 +4983,10 @@
         <v>78</v>
       </c>
       <c r="R79" t="s">
-        <v>227</v>
+        <v>483</v>
       </c>
       <c r="S79" t="s">
-        <v>228</v>
+        <v>484</v>
       </c>
       <c r="T79" t="s">
         <v>432</v>
@@ -5069,10 +5021,10 @@
         <v>78</v>
       </c>
       <c r="R80" t="s">
-        <v>412</v>
+        <v>82</v>
       </c>
       <c r="S80" t="s">
-        <v>413</v>
+        <v>83</v>
       </c>
       <c r="T80" t="s">
         <v>432</v>
@@ -5107,10 +5059,10 @@
         <v>78</v>
       </c>
       <c r="R81" t="s">
-        <v>477</v>
+        <v>362</v>
       </c>
       <c r="S81" t="s">
-        <v>478</v>
+        <v>363</v>
       </c>
       <c r="T81" t="s">
         <v>432</v>
@@ -5145,10 +5097,10 @@
         <v>78</v>
       </c>
       <c r="R82" t="s">
-        <v>235</v>
+        <v>485</v>
       </c>
       <c r="S82" t="s">
-        <v>236</v>
+        <v>486</v>
       </c>
       <c r="T82" t="s">
         <v>432</v>
@@ -5183,10 +5135,10 @@
         <v>78</v>
       </c>
       <c r="R83" t="s">
-        <v>479</v>
+        <v>102</v>
       </c>
       <c r="S83" t="s">
-        <v>480</v>
+        <v>103</v>
       </c>
       <c r="T83" t="s">
         <v>432</v>
@@ -5221,10 +5173,10 @@
         <v>78</v>
       </c>
       <c r="R84" t="s">
-        <v>165</v>
+        <v>112</v>
       </c>
       <c r="S84" t="s">
-        <v>166</v>
+        <v>113</v>
       </c>
       <c r="T84" t="s">
         <v>432</v>
@@ -5259,10 +5211,10 @@
         <v>78</v>
       </c>
       <c r="R85" t="s">
-        <v>481</v>
+        <v>118</v>
       </c>
       <c r="S85" t="s">
-        <v>482</v>
+        <v>119</v>
       </c>
       <c r="T85" t="s">
         <v>432</v>
@@ -5281,18 +5233,6 @@
       <c r="O86" t="s">
         <v>289</v>
       </c>
-      <c r="Q86" t="s">
-        <v>78</v>
-      </c>
-      <c r="R86" t="s">
-        <v>483</v>
-      </c>
-      <c r="S86" t="s">
-        <v>484</v>
-      </c>
-      <c r="T86" t="s">
-        <v>432</v>
-      </c>
     </row>
     <row r="87" spans="7:20" x14ac:dyDescent="0.45">
       <c r="L87" t="s">
@@ -5307,18 +5247,6 @@
       <c r="O87" t="s">
         <v>289</v>
       </c>
-      <c r="Q87" t="s">
-        <v>78</v>
-      </c>
-      <c r="R87" t="s">
-        <v>485</v>
-      </c>
-      <c r="S87" t="s">
-        <v>486</v>
-      </c>
-      <c r="T87" t="s">
-        <v>432</v>
-      </c>
     </row>
     <row r="88" spans="7:20" x14ac:dyDescent="0.45">
       <c r="L88" t="s">
@@ -5333,18 +5261,6 @@
       <c r="O88" t="s">
         <v>289</v>
       </c>
-      <c r="Q88" t="s">
-        <v>78</v>
-      </c>
-      <c r="R88" t="s">
-        <v>487</v>
-      </c>
-      <c r="S88" t="s">
-        <v>488</v>
-      </c>
-      <c r="T88" t="s">
-        <v>432</v>
-      </c>
     </row>
     <row r="89" spans="7:20" x14ac:dyDescent="0.45">
       <c r="L89" t="s">
@@ -5359,18 +5275,6 @@
       <c r="O89" t="s">
         <v>289</v>
       </c>
-      <c r="Q89" t="s">
-        <v>78</v>
-      </c>
-      <c r="R89" t="s">
-        <v>424</v>
-      </c>
-      <c r="S89" t="s">
-        <v>425</v>
-      </c>
-      <c r="T89" t="s">
-        <v>432</v>
-      </c>
     </row>
     <row r="90" spans="7:20" x14ac:dyDescent="0.45">
       <c r="L90" t="s">
@@ -5385,18 +5289,6 @@
       <c r="O90" t="s">
         <v>289</v>
       </c>
-      <c r="Q90" t="s">
-        <v>78</v>
-      </c>
-      <c r="R90" t="s">
-        <v>489</v>
-      </c>
-      <c r="S90" t="s">
-        <v>490</v>
-      </c>
-      <c r="T90" t="s">
-        <v>432</v>
-      </c>
     </row>
     <row r="91" spans="7:20" x14ac:dyDescent="0.45">
       <c r="L91" t="s">
@@ -5411,18 +5303,6 @@
       <c r="O91" t="s">
         <v>289</v>
       </c>
-      <c r="Q91" t="s">
-        <v>78</v>
-      </c>
-      <c r="R91" t="s">
-        <v>491</v>
-      </c>
-      <c r="S91" t="s">
-        <v>492</v>
-      </c>
-      <c r="T91" t="s">
-        <v>432</v>
-      </c>
     </row>
     <row r="92" spans="7:20" x14ac:dyDescent="0.45">
       <c r="L92" t="s">
@@ -5437,18 +5317,6 @@
       <c r="O92" t="s">
         <v>289</v>
       </c>
-      <c r="Q92" t="s">
-        <v>78</v>
-      </c>
-      <c r="R92" t="s">
-        <v>292</v>
-      </c>
-      <c r="S92" t="s">
-        <v>293</v>
-      </c>
-      <c r="T92" t="s">
-        <v>432</v>
-      </c>
     </row>
     <row r="93" spans="7:20" x14ac:dyDescent="0.45">
       <c r="L93" t="s">
@@ -5463,18 +5331,6 @@
       <c r="O93" t="s">
         <v>289</v>
       </c>
-      <c r="Q93" t="s">
-        <v>78</v>
-      </c>
-      <c r="R93" t="s">
-        <v>493</v>
-      </c>
-      <c r="S93" t="s">
-        <v>494</v>
-      </c>
-      <c r="T93" t="s">
-        <v>432</v>
-      </c>
     </row>
     <row r="94" spans="7:20" x14ac:dyDescent="0.45">
       <c r="L94" t="s">
@@ -5489,18 +5345,6 @@
       <c r="O94" t="s">
         <v>289</v>
       </c>
-      <c r="Q94" t="s">
-        <v>78</v>
-      </c>
-      <c r="R94" t="s">
-        <v>82</v>
-      </c>
-      <c r="S94" t="s">
-        <v>83</v>
-      </c>
-      <c r="T94" t="s">
-        <v>432</v>
-      </c>
     </row>
     <row r="95" spans="7:20" x14ac:dyDescent="0.45">
       <c r="L95" t="s">
@@ -5515,18 +5359,6 @@
       <c r="O95" t="s">
         <v>289</v>
       </c>
-      <c r="Q95" t="s">
-        <v>78</v>
-      </c>
-      <c r="R95" t="s">
-        <v>362</v>
-      </c>
-      <c r="S95" t="s">
-        <v>363</v>
-      </c>
-      <c r="T95" t="s">
-        <v>432</v>
-      </c>
     </row>
     <row r="96" spans="7:20" x14ac:dyDescent="0.45">
       <c r="L96" t="s">
@@ -5541,20 +5373,8 @@
       <c r="O96" t="s">
         <v>289</v>
       </c>
-      <c r="Q96" t="s">
-        <v>78</v>
-      </c>
-      <c r="R96" t="s">
-        <v>316</v>
-      </c>
-      <c r="S96" t="s">
-        <v>317</v>
-      </c>
-      <c r="T96" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="97" spans="12:20" x14ac:dyDescent="0.45">
+    </row>
+    <row r="97" spans="12:15" x14ac:dyDescent="0.45">
       <c r="L97" t="s">
         <v>78</v>
       </c>
@@ -5567,20 +5387,8 @@
       <c r="O97" t="s">
         <v>289</v>
       </c>
-      <c r="Q97" t="s">
-        <v>78</v>
-      </c>
-      <c r="R97" t="s">
-        <v>138</v>
-      </c>
-      <c r="S97" t="s">
-        <v>139</v>
-      </c>
-      <c r="T97" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="98" spans="12:20" x14ac:dyDescent="0.45">
+    </row>
+    <row r="98" spans="12:15" x14ac:dyDescent="0.45">
       <c r="L98" t="s">
         <v>78</v>
       </c>
@@ -5593,20 +5401,8 @@
       <c r="O98" t="s">
         <v>289</v>
       </c>
-      <c r="Q98" t="s">
-        <v>78</v>
-      </c>
-      <c r="R98" t="s">
-        <v>495</v>
-      </c>
-      <c r="S98" t="s">
-        <v>496</v>
-      </c>
-      <c r="T98" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="99" spans="12:20" x14ac:dyDescent="0.45">
+    </row>
+    <row r="99" spans="12:15" x14ac:dyDescent="0.45">
       <c r="L99" t="s">
         <v>78</v>
       </c>
@@ -5619,20 +5415,8 @@
       <c r="O99" t="s">
         <v>289</v>
       </c>
-      <c r="Q99" t="s">
-        <v>78</v>
-      </c>
-      <c r="R99" t="s">
-        <v>102</v>
-      </c>
-      <c r="S99" t="s">
-        <v>103</v>
-      </c>
-      <c r="T99" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="100" spans="12:20" x14ac:dyDescent="0.45">
+    </row>
+    <row r="100" spans="12:15" x14ac:dyDescent="0.45">
       <c r="L100" t="s">
         <v>78</v>
       </c>
@@ -5645,20 +5429,8 @@
       <c r="O100" t="s">
         <v>289</v>
       </c>
-      <c r="Q100" t="s">
-        <v>78</v>
-      </c>
-      <c r="R100" t="s">
-        <v>112</v>
-      </c>
-      <c r="S100" t="s">
-        <v>113</v>
-      </c>
-      <c r="T100" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="101" spans="12:20" x14ac:dyDescent="0.45">
+    </row>
+    <row r="101" spans="12:15" x14ac:dyDescent="0.45">
       <c r="L101" t="s">
         <v>78</v>
       </c>
@@ -5671,20 +5443,8 @@
       <c r="O101" t="s">
         <v>289</v>
       </c>
-      <c r="Q101" t="s">
-        <v>78</v>
-      </c>
-      <c r="R101" t="s">
-        <v>497</v>
-      </c>
-      <c r="S101" t="s">
-        <v>498</v>
-      </c>
-      <c r="T101" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="102" spans="12:20" x14ac:dyDescent="0.45">
+    </row>
+    <row r="102" spans="12:15" x14ac:dyDescent="0.45">
       <c r="L102" t="s">
         <v>78</v>
       </c>
@@ -5697,20 +5457,8 @@
       <c r="O102" t="s">
         <v>289</v>
       </c>
-      <c r="Q102" t="s">
-        <v>78</v>
-      </c>
-      <c r="R102" t="s">
-        <v>128</v>
-      </c>
-      <c r="S102" t="s">
-        <v>129</v>
-      </c>
-      <c r="T102" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="103" spans="12:20" x14ac:dyDescent="0.45">
+    </row>
+    <row r="103" spans="12:15" x14ac:dyDescent="0.45">
       <c r="L103" t="s">
         <v>78</v>
       </c>
@@ -5723,20 +5471,8 @@
       <c r="O103" t="s">
         <v>289</v>
       </c>
-      <c r="Q103" t="s">
-        <v>78</v>
-      </c>
-      <c r="R103" t="s">
-        <v>118</v>
-      </c>
-      <c r="S103" t="s">
-        <v>119</v>
-      </c>
-      <c r="T103" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="104" spans="12:20" x14ac:dyDescent="0.45">
+    </row>
+    <row r="104" spans="12:15" x14ac:dyDescent="0.45">
       <c r="L104" t="s">
         <v>78</v>
       </c>
@@ -5749,20 +5485,8 @@
       <c r="O104" t="s">
         <v>289</v>
       </c>
-      <c r="Q104" t="s">
-        <v>78</v>
-      </c>
-      <c r="R104" t="s">
-        <v>499</v>
-      </c>
-      <c r="S104" t="s">
-        <v>500</v>
-      </c>
-      <c r="T104" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="105" spans="12:20" x14ac:dyDescent="0.45">
+    </row>
+    <row r="105" spans="12:15" x14ac:dyDescent="0.45">
       <c r="L105" t="s">
         <v>78</v>
       </c>
@@ -5775,20 +5499,8 @@
       <c r="O105" t="s">
         <v>289</v>
       </c>
-      <c r="Q105" t="s">
-        <v>78</v>
-      </c>
-      <c r="R105" t="s">
-        <v>501</v>
-      </c>
-      <c r="S105" t="s">
-        <v>502</v>
-      </c>
-      <c r="T105" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="106" spans="12:20" x14ac:dyDescent="0.45">
+    </row>
+    <row r="106" spans="12:15" x14ac:dyDescent="0.45">
       <c r="L106" t="s">
         <v>78</v>
       </c>
@@ -5802,7 +5514,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="107" spans="12:20" x14ac:dyDescent="0.45">
+    <row r="107" spans="12:15" x14ac:dyDescent="0.45">
       <c r="L107" t="s">
         <v>78</v>
       </c>
@@ -5816,7 +5528,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="108" spans="12:20" x14ac:dyDescent="0.45">
+    <row r="108" spans="12:15" x14ac:dyDescent="0.45">
       <c r="L108" t="s">
         <v>78</v>
       </c>
@@ -5830,7 +5542,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="109" spans="12:20" x14ac:dyDescent="0.45">
+    <row r="109" spans="12:15" x14ac:dyDescent="0.45">
       <c r="L109" t="s">
         <v>78</v>
       </c>
@@ -5844,7 +5556,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="110" spans="12:20" x14ac:dyDescent="0.45">
+    <row r="110" spans="12:15" x14ac:dyDescent="0.45">
       <c r="L110" t="s">
         <v>78</v>
       </c>
@@ -5858,7 +5570,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="111" spans="12:20" x14ac:dyDescent="0.45">
+    <row r="111" spans="12:15" x14ac:dyDescent="0.45">
       <c r="L111" t="s">
         <v>78</v>
       </c>
@@ -5872,7 +5584,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="112" spans="12:20" x14ac:dyDescent="0.45">
+    <row r="112" spans="12:15" x14ac:dyDescent="0.45">
       <c r="L112" t="s">
         <v>78</v>
       </c>
